--- a/Aminolab.xlsx
+++ b/Aminolab.xlsx
@@ -7,14 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check4" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check5" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check1_1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check2_2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check3_3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check4_4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check5_5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check6_6" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Check7_7" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,9 +431,1359 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>values</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TEMPERATURE CENTIGRADE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>celsius</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TURBIDITY NTU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NTU</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DISSOLVED OXYGEN AS O2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PH MEASURED IN FIELD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REDOX</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mV</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FIELD ELECTRICAL CONDUCTIVITY</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>mS/cm</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>OIL LAYER THICKNESS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CALCIUM AS CA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MAGNESIUM AS MG</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SODIUM AS NA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>POTASSIUM AS K</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CHLORIDE AS CL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SULFATE AS SO4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BICARBONATE AS HCO3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NITRATE AS NO3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BORON AS B</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FLUORIDE AS F</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BROMIDE AS BR</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PHOSPHATE AS PO4</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TOTAL ORGANIC CARBON (TOC)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TOTAL NITROGEN AS N</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ALUMINUM (Al)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SILVER (Ag)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ARSENIC AS AS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BARIUM AS BA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BERYLIUM (Be)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ANTIMONY (Sb)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CADMIUM AS CD</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CYANIDE AS CN</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>COBALT AS CO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CHROMIUM AS CR</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>COPPER AS CU</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>FERROUS IRON DISSOLVED AS FE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MERCURY AS HG</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MANGANESE TOTAL AS MN</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NICKEL AS NI</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LEAD AS PB</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SELENIUM AS SE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ZINC AS ZN</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MTBE</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TERTIARY BUTYL ALCOHOL</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BENZENE</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ETHYL BENZENE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TOLUENE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>XYLENE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DICHLORODIFLUOROMETHANE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CHLOROMETHANE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>VINYL CHLORIDE (VC)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CHLOROETHANE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TRICHLOROFLUOROMETHANE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DICHLOROETHYLENE 1,1 (1,1 DCE)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>METHYLENE CHLORIDE (DCM)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TRANS-1,2 DICHLOROETHYLENE (T1,2 DCE)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1,1-DICHLOROETHANE (1,1 DCA)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CIS 1,2 DICHLOROETHYLENE (C1,2 DCE)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CHLOROFORM</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TRICHLORO ETHANE 1,1,1 (1,1,1 TCA)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CARBON TETRACHLORIDE</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1,3-DICHLOROBENZENE</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>DICHLOROETHANE1,2</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TRICHLOROETHYLENE (TCE)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1,2-DICHLOROPROPANE</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>DIBROMOMETHANE</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1,1,2-TRICHLOROETHANE (1,1,2 TCA)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TETRACHLOROETHYLENE (PCE)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>DIBROMOCHLOROMETHANE</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ETHYLENE DIBROMIDE (EDB)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MONOCHLOROBENZENE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>STYRENE</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BROMOBENZENE</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1,2,3-TRICHLOROPROPANE (TCP)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1,3,5 TRIMETHYLBENZENE (MESITYLENE)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1,2,4 TRIMETHYLBENZENE</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1,4 DICHLOROBENZENE (1,4 DCB)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1,2 DICHLOROBENZENE (ODCB)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1,2-DIBROMO-3-CHLOROPROPANE (DBCP)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1,2,4-TRICHLOROBENZENE</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>NAPTHALENE</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1,2,3-TRICHLOROBENZENE</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1,1,1,2-TETRACHLOROETHANE</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1,1,2,2-TETRACHLOROETHANE</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1,1-DICHLOROPROPENE</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BROMOMETHANE</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>DIBROMOCHLOROMETHANE</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1,1-DICHLOROPROPENE</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>DIBROMOCHLOROMETHANE</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ACETONE</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>TRIBROMOMETHANE (BROMOFORM)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>DICHLOROBROMOMETHANE</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>FORMALDEHYDE</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1,4 DIOXANE</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>PERCHLORATE</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TOTAL PETROLEUM HYDROCARBONS (TPH)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>POLYAROMATIC HYDROCARBONS (PAH)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>µg/L</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -489,11 +1838,7 @@
           <t>NTU</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -572,7 +1917,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
@@ -587,7 +1932,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25.2</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="11">
@@ -602,7 +1947,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>99.5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -617,7 +1962,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="13">
@@ -632,7 +1977,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -647,7 +1992,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -662,7 +2007,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>231</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16">
@@ -677,7 +2022,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -692,7 +2037,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>266</v>
+        <v>347</v>
       </c>
     </row>
     <row r="18">
@@ -766,10 +2111,8 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C22" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -829,7 +2172,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27">
@@ -858,10 +2201,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C28" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="29">
@@ -890,11 +2231,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -907,11 +2244,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1000,7 +2333,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1030,7 +2363,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="40">
@@ -1045,7 +2378,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41">
@@ -1059,10 +2392,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -1104,11 +2435,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1179,9 +2506,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="C49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1222,10 +2547,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -1239,11 +2562,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1271,11 +2590,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1318,11 +2633,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1363,10 +2674,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C61" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="62">
@@ -1395,9 +2704,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v>5</v>
-      </c>
+      <c r="C63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1410,11 +2717,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1427,11 +2730,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1444,10 +2743,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -1461,11 +2758,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1478,11 +2771,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1555,11 +2844,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1572,11 +2857,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1634,11 +2915,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1651,11 +2928,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1668,11 +2941,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1730,11 +2999,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1747,11 +3012,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1779,11 +3040,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1809,11 +3066,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1948,11 +3201,7 @@
           <t>NTU</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2031,7 +3280,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10">
@@ -2046,7 +3295,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25.9</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="11">
@@ -2061,7 +3310,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>107</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2076,7 +3325,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
@@ -2091,7 +3340,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -2106,7 +3355,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +3370,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>244</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16">
@@ -2136,7 +3385,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17">
@@ -2151,7 +3400,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>347</v>
+        <v>382</v>
       </c>
     </row>
     <row r="18">
@@ -2225,10 +3474,8 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C22" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -2288,7 +3535,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27">
@@ -2317,10 +3564,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C28" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="29">
@@ -2349,11 +3594,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2366,11 +3607,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2489,7 +3726,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="40">
@@ -2518,10 +3755,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -2563,11 +3798,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2638,9 +3869,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="C49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2681,10 +3910,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2698,11 +3925,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2730,11 +3953,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2777,11 +3996,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2822,10 +4037,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C61" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="62">
@@ -2854,9 +4067,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v>5</v>
-      </c>
+      <c r="C63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2869,11 +4080,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2886,11 +4093,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2903,10 +4106,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2920,11 +4121,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2937,11 +4134,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3014,11 +4207,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3031,11 +4220,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3093,11 +4278,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3110,11 +4291,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3127,11 +4304,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3189,11 +4362,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3206,11 +4375,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3238,11 +4403,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3268,11 +4429,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3407,11 +4564,7 @@
           <t>NTU</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3490,7 +4643,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>146</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10">
@@ -3505,7 +4658,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27.6</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="11">
@@ -3520,7 +4673,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>99.09999999999999</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -3535,7 +4688,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -3550,7 +4703,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -3565,7 +4718,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
@@ -3580,7 +4733,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>263</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16">
@@ -3610,7 +4763,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>382</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18">
@@ -3670,7 +4823,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="22">
@@ -3684,10 +4837,8 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C22" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -3747,7 +4898,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27">
@@ -3776,10 +4927,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C28" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="29">
@@ -3808,11 +4957,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3825,11 +4970,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3977,10 +5118,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -4022,11 +5161,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4097,9 +5232,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="C49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4140,10 +5273,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -4157,11 +5288,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4189,11 +5316,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4236,11 +5359,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4281,10 +5400,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C61" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="62">
@@ -4313,9 +5430,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v>5</v>
-      </c>
+      <c r="C63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4328,11 +5443,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4345,11 +5456,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4362,10 +5469,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4379,11 +5484,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4396,11 +5497,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4473,11 +5570,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4490,11 +5583,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4552,11 +5641,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4569,11 +5654,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4586,11 +5667,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4648,11 +5725,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4665,11 +5738,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4697,11 +5766,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4727,11 +5792,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4866,11 +5927,7 @@
           <t>NTU</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4949,7 +6006,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
@@ -4964,7 +6021,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27.1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -4979,7 +6036,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>99.59999999999999</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -5009,7 +6066,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
@@ -5024,7 +6081,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
@@ -5039,7 +6096,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16">
@@ -5069,7 +6126,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="18">
@@ -5129,7 +6186,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="22">
@@ -5143,10 +6200,8 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C22" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -5206,7 +6261,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27">
@@ -5235,10 +6290,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C28" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="29">
@@ -5267,11 +6320,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5284,11 +6333,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5302,7 +6347,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="33">
@@ -5407,7 +6452,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="40">
@@ -5436,10 +6481,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -5481,11 +6524,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5556,9 +6595,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="C49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5599,10 +6636,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -5616,11 +6651,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5648,11 +6679,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5695,11 +6722,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5740,10 +6763,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C61" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="62">
@@ -5772,9 +6793,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v>5</v>
-      </c>
+      <c r="C63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5787,11 +6806,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5804,11 +6819,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5821,10 +6832,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -5838,11 +6847,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5855,11 +6860,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5932,11 +6933,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5949,11 +6946,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6011,11 +7004,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6028,11 +7017,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6045,11 +7030,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6107,11 +7088,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6124,11 +7101,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6156,11 +7129,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6186,11 +7155,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6325,11 +7290,7 @@
           <t>NTU</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6408,7 +7369,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -6423,7 +7384,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="11">
@@ -6438,7 +7399,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -6453,7 +7414,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="13">
@@ -6483,7 +7444,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
@@ -6498,7 +7459,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16">
@@ -6528,7 +7489,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>308</v>
+        <v>266</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +7563,8 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C22" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -6694,10 +7653,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C28" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="29">
@@ -6726,11 +7683,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6743,11 +7696,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6761,7 +7710,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="33">
@@ -6836,7 +7785,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="38">
@@ -6866,7 +7815,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="40">
@@ -6895,10 +7844,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -6940,11 +7887,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7015,9 +7958,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="C49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7058,10 +7999,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -7075,11 +8014,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7107,11 +8042,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7154,11 +8085,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7199,10 +8126,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C61" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="62">
@@ -7231,9 +8156,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v>5</v>
-      </c>
+      <c r="C63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7246,11 +8169,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7263,11 +8182,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7280,10 +8195,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -7297,11 +8210,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7314,11 +8223,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7391,11 +8296,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7408,11 +8309,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7470,11 +8367,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7487,11 +8380,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7504,11 +8393,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7566,11 +8451,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7583,11 +8464,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7615,11 +8492,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7645,11 +8518,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7784,11 +8653,7 @@
           <t>NTU</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7867,7 +8732,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10">
@@ -7882,7 +8747,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24.3</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="11">
@@ -7897,7 +8762,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -7912,7 +8777,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="13">
@@ -7927,7 +8792,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -7942,7 +8807,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15">
@@ -7957,7 +8822,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>246</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16">
@@ -7987,7 +8852,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>266</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18">
@@ -8061,10 +8926,8 @@
           <t>mg/L</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C22" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -8124,7 +8987,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>108</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -8153,10 +9016,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C28" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="29">
@@ -8185,11 +9046,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8202,11 +9059,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8220,7 +9073,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="33">
@@ -8295,7 +9148,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -8325,7 +9178,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="40">
@@ -8354,10 +9207,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -8399,11 +9250,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -8474,9 +9321,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C49" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="C49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8517,10 +9362,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -8534,11 +9377,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8566,11 +9405,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8613,11 +9448,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8658,10 +9489,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C61" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="62">
@@ -8690,9 +9519,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C63" t="n">
-        <v>5</v>
-      </c>
+      <c r="C63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8705,11 +9532,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8722,11 +9545,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8739,10 +9558,8 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
+      <c r="C66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -8756,11 +9573,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8773,11 +9586,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8850,11 +9659,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8867,11 +9672,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8929,11 +9730,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8946,11 +9743,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8963,11 +9756,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9025,11 +9814,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9042,11 +9827,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9074,11 +9855,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9104,1470 +9881,7 @@
           <t>µg/L</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>DICHLOROBROMOMETHANE</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>FORMALDEHYDE</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>1,4 DIOXANE</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>PERCHLORATE</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>TOTAL PETROLEUM HYDROCARBONS (TPH)</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>POLYAROMATIC HYDROCARBONS (PAH)</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C95"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>values</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TEMPERATURE CENTIGRADE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>celsius</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TURBIDITY NTU</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NTU</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DISSOLVED OXYGEN AS O2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PH MEASURED IN FIELD</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REDOX</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>mV</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>FIELD ELECTRICAL CONDUCTIVITY</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>mS/cm</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>OIL LAYER THICKNESS</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>cm</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CALCIUM AS CA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MAGNESIUM AS MG</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>27.1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SODIUM AS NA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>POTASSIUM AS K</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CHLORIDE AS CL</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SULFATE AS SO4</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>BICARBONATE AS HCO3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NITRATE AS NO3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>BORON AS B</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>FLUORIDE AS F</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>BROMIDE AS BR</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>PHOSPHATE AS PO4</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TOTAL ORGANIC CARBON (TOC)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TOTAL NITROGEN AS N</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>mg/L</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ALUMINUM (Al)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>SILVER (Ag)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ARSENIC AS AS</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>BARIUM AS BA</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>95.59999999999999</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>BERYLIUM (Be)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>ANTIMONY (Sb)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>CADMIUM AS CD</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>CYANIDE AS CN</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>COBALT AS CO</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>CHROMIUM AS CR</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>COPPER AS CU</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>FERROUS IRON DISSOLVED AS FE</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>MERCURY AS HG</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>0.0002</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>MANGANESE TOTAL AS MN</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>NICKEL AS NI</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>LEAD AS PB</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>SELENIUM AS SE</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>ZINC AS ZN</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>MTBE</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>TERTIARY BUTYL ALCOHOL</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>BENZENE</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>ETHYL BENZENE</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>TOLUENE</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>XYLENE</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>DICHLORODIFLUOROMETHANE</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>CHLOROMETHANE</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>VINYL CHLORIDE (VC)</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>CHLOROETHANE</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>TRICHLOROFLUOROMETHANE</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>DICHLOROETHYLENE 1,1 (1,1 DCE)</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>METHYLENE CHLORIDE (DCM)</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>TRANS-1,2 DICHLOROETHYLENE (T1,2 DCE)</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>1,1-DICHLOROETHANE (1,1 DCA)</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>CIS 1,2 DICHLOROETHYLENE (C1,2 DCE)</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>CHLOROFORM</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>TRICHLORO ETHANE 1,1,1 (1,1,1 TCA)</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>CARBON TETRACHLORIDE</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>1,3-DICHLOROBENZENE</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>DICHLOROETHANE1,2</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>TRICHLOROETHYLENE (TCE)</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>1,2-DICHLOROPROPANE</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>DIBROMOMETHANE</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>1,1,2-TRICHLOROETHANE (1,1,2 TCA)</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>TETRACHLOROETHYLENE (PCE)</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>DIBROMOCHLOROMETHANE</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>ETHYLENE DIBROMIDE (EDB)</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>MONOCHLOROBENZENE</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>STYRENE</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>BROMOBENZENE</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>1,2,3-TRICHLOROPROPANE (TCP)</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>1,3,5 TRIMETHYLBENZENE (MESITYLENE)</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>1,2,4 TRIMETHYLBENZENE</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>1,4 DICHLOROBENZENE (1,4 DCB)</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>1,2 DICHLOROBENZENE (ODCB)</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>1,2-DIBROMO-3-CHLOROPROPANE (DBCP)</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>1,2,4-TRICHLOROBENZENE</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>NAPTHALENE</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>1,2,3-TRICHLOROBENZENE</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>1,1,1,2-TETRACHLOROETHANE</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>1,1,2,2-TETRACHLOROETHANE</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>1,1-DICHLOROPROPENE</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>BROMOMETHANE</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>DIBROMOCHLOROMETHANE</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>1,1-DICHLOROPROPENE</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>DIBROMOCHLOROMETHANE</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>ACETONE</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>TRIBROMOMETHANE (BROMOFORM)</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>µg/L</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Not detected</t>
-        </is>
-      </c>
+      <c r="C89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
